--- a/scenario1/XLSX Files/Scenario_1/Scenario_1_meanNER-vs-p.xlsx
+++ b/scenario1/XLSX Files/Scenario_1/Scenario_1_meanNER-vs-p.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,28 +493,28 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3101234567901234</v>
+        <v>0.3129629629629629</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3602469135802469</v>
+        <v>0.3574074074074074</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5293827160493827</v>
+        <v>0.5313580246913581</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7593827160493827</v>
+        <v>0.754320987654321</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9401234567901234</v>
+        <v>0.9398765432098766</v>
       </c>
       <c r="I2" t="n">
         <v>0.1685185185185185</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5854320987654321</v>
+        <v>0.5834567901234567</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8060493827160494</v>
+        <v>0.811358024691358</v>
       </c>
     </row>
     <row r="3">
@@ -530,28 +530,28 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D3" t="n">
-        <v>0.358641975308642</v>
+        <v>0.3065432098765432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2177777777777778</v>
+        <v>0.2349382716049383</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6861728395061728</v>
+        <v>0.6912345679012346</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5909876543209877</v>
+        <v>0.6049382716049383</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9158024691358024</v>
+        <v>0.9193827160493827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2791358024691358</v>
+        <v>0.3114814814814815</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5539506172839506</v>
+        <v>0.5379012345679013</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8567901234567901</v>
+        <v>0.8528395061728395</v>
       </c>
     </row>
     <row r="4">
@@ -564,31 +564,31 @@
         <v>200</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06111111111111111</v>
+        <v>0.05740740740740741</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3677777777777778</v>
+        <v>0.3561728395061728</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3025925925925926</v>
+        <v>0.3141975308641975</v>
       </c>
       <c r="F4" t="n">
         <v>0.5018518518518519</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8232098765432099</v>
+        <v>0.8222222222222222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9079012345679013</v>
+        <v>0.9051851851851852</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1648148148148148</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="J4" t="n">
         <v>0.6129629629629629</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7744444444444445</v>
+        <v>0.7781481481481481</v>
       </c>
     </row>
     <row r="5">
@@ -601,31 +601,31 @@
         <v>500</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2633333333333333</v>
+        <v>0.2641975308641975</v>
       </c>
       <c r="D5" t="n">
-        <v>0.812962962962963</v>
+        <v>0.720246913580247</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1848148148148148</v>
+        <v>0.1840740740740741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3967901234567901</v>
+        <v>0.4130864197530864</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7934567901234568</v>
+        <v>0.8167901234567901</v>
       </c>
       <c r="H5" t="n">
-        <v>0.798395061728395</v>
+        <v>0.8209876543209876</v>
       </c>
       <c r="I5" t="n">
         <v>0.05740740740740741</v>
       </c>
       <c r="J5" t="n">
-        <v>0.512962962962963</v>
+        <v>0.5277777777777778</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6965432098765432</v>
+        <v>0.7120987654320987</v>
       </c>
     </row>
     <row r="6">
@@ -641,28 +641,28 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4202469135802469</v>
+        <v>0.4208641975308642</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7865432098765432</v>
+        <v>0.7930864197530865</v>
       </c>
       <c r="F6" t="n">
         <v>0.1685185185185185</v>
       </c>
       <c r="G6" t="n">
-        <v>0.47</v>
+        <v>0.4719753086419753</v>
       </c>
       <c r="H6" t="n">
         <v>0.9449382716049383</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7724691358024691</v>
+        <v>0.7661728395061729</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2827160493827161</v>
+        <v>0.2797530864197531</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6138271604938271</v>
+        <v>0.6139506172839506</v>
       </c>
     </row>
     <row r="7">
@@ -678,28 +678,28 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D7" t="n">
-        <v>0.501358024691358</v>
+        <v>0.5369135802469136</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2801234567901235</v>
+        <v>0.2818518518518519</v>
       </c>
       <c r="F7" t="n">
         <v>0.1741975308641975</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6153086419753087</v>
+        <v>0.6272839506172839</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8828395061728395</v>
+        <v>0.8965432098765432</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4949382716049383</v>
+        <v>0.4520987654320988</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6119753086419754</v>
+        <v>0.6082716049382716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8985185185185185</v>
+        <v>0.8820987654320988</v>
       </c>
     </row>
     <row r="8">
@@ -715,7 +715,7 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3917283950617284</v>
+        <v>0.3922222222222222</v>
       </c>
       <c r="E8" t="n">
         <v>0.8332098765432099</v>
@@ -724,7 +724,7 @@
         <v>0.1685185185185185</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5067901234567901</v>
+        <v>0.5090123456790123</v>
       </c>
       <c r="H8" t="n">
         <v>0.9462962962962963</v>
@@ -736,7 +736,7 @@
         <v>0.2796296296296296</v>
       </c>
       <c r="K8" t="n">
-        <v>0.607037037037037</v>
+        <v>0.604320987654321</v>
       </c>
     </row>
     <row r="9">
@@ -767,19 +767,19 @@
         <v>0.9462962962962963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5987654320987654</v>
+        <v>0.5764197530864198</v>
       </c>
       <c r="J9" t="n">
         <v>0.2796296296296296</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5160493827160494</v>
+        <v>0.538395061728395</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>PA-1-100</t>
+          <t>Griewank-100</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -789,34 +789,34 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4202469135802469</v>
+        <v>0.4797530864197531</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7879012345679013</v>
+        <v>0.4128395061728395</v>
       </c>
       <c r="F10" t="n">
+        <v>0.2796296296296296</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7240740740740741</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9449382716049383</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.1685185185185185</v>
       </c>
-      <c r="G10" t="n">
-        <v>0.4723456790123457</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9461728395061728</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.7707407407407407</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.2796296296296296</v>
+        <v>0.6129629629629629</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6137037037037038</v>
+        <v>0.8365432098765432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>PA-1-20</t>
+          <t>Griewank-20</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -826,108 +826,108 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4818518518518519</v>
+        <v>0.462962962962963</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2783950617283951</v>
+        <v>0.262716049382716</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1759259259259259</v>
+        <v>0.3303703703703704</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5496296296296296</v>
+        <v>0.6777777777777778</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8883950617283951</v>
+        <v>0.8988888888888888</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6491358024691358</v>
+        <v>0.2846913580246914</v>
       </c>
       <c r="J11" t="n">
-        <v>0.554320987654321</v>
+        <v>0.6592592592592592</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8816049382716049</v>
+        <v>0.8825925925925926</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>PA-1-200</t>
+          <t>Griewank-200</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>200</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05740740740740741</v>
+        <v>0.1609876543209877</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3949382716049383</v>
+        <v>0.5017283950617284</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8338271604938272</v>
+        <v>0.3908641975308642</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.2796296296296296</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5065432098765432</v>
+        <v>0.7622222222222222</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9462962962962963</v>
+        <v>0.9335802469135802</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7254320987654321</v>
+        <v>0.06493827160493827</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2796296296296296</v>
+        <v>0.6129629629629629</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6040740740740741</v>
+        <v>0.8097530864197531</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>PA-1-500</t>
+          <t>Griewank-500</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>500</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05740740740740741</v>
+        <v>0.562962962962963</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3907407407407407</v>
+        <v>0.3916049382716049</v>
       </c>
       <c r="E13" t="n">
-        <v>0.725925925925926</v>
+        <v>0.1723456790123457</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.2758024691358025</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8307407407407408</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9462962962962963</v>
+        <v>0.908641975308642</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5832098765432099</v>
+        <v>0.05740740740740741</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2796296296296296</v>
+        <v>0.5509876543209876</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5316049382716049</v>
+        <v>0.7661728395061729</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>PA-10-100</t>
+          <t>PA-1-100</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -937,34 +937,34 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4932098765432099</v>
+        <v>0.4107407407407407</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7208641975308642</v>
+        <v>0.7834567901234568</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8346913580246914</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.4811111111111111</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2796296296296296</v>
+        <v>0.9461728395061728</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9462962962962963</v>
+        <v>0.7749382716049382</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.2803703703703704</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3993827160493827</v>
+        <v>0.6139506172839506</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>PA-10-20</t>
+          <t>PA-1-20</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -974,34 +974,34 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D15" t="n">
-        <v>0.692716049382716</v>
+        <v>0.4933333333333333</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5265432098765432</v>
+        <v>0.2834567901234568</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8351851851851851</v>
+        <v>0.1795061728395062</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.5530864197530865</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3118518518518518</v>
+        <v>0.8887654320987655</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9462962962962963</v>
+        <v>0.5982716049382716</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6196296296296296</v>
+        <v>0.572962962962963</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3585185185185185</v>
+        <v>0.8898765432098765</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>PA-10-200</t>
+          <t>PA-1-200</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1011,34 +1011,34 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4817283950617284</v>
+        <v>0.4004938271604938</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7951851851851852</v>
+        <v>0.8337037037037037</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7640740740740741</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.5003703703703704</v>
       </c>
       <c r="H16" t="n">
+        <v>0.9462962962962963</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7255555555555555</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.2796296296296296</v>
       </c>
-      <c r="I16" t="n">
-        <v>0.9462962962962963</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.6129629629629629</v>
-      </c>
       <c r="K16" t="n">
-        <v>0.4108641975308642</v>
+        <v>0.6046913580246913</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>PA-10-500</t>
+          <t>PA-1-500</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1048,324 +1048,620 @@
         <v>0.05740740740740741</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4961728395061729</v>
+        <v>0.3907407407407407</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8351851851851851</v>
+        <v>0.725925925925926</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7240740740740741</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1861728395061728</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2619753086419753</v>
+        <v>0.9462962962962963</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9462962962962963</v>
+        <v>0.5797530864197531</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6129629629629629</v>
+        <v>0.2796296296296296</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3964197530864197</v>
+        <v>0.5350617283950617</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Rastrigin-100</t>
+          <t>PA-10-100</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>100</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3911111111111111</v>
+        <v>0.05740740740740741</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2808641975308642</v>
+        <v>0.5007407407407407</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4981481481481481</v>
+        <v>0.7208641975308642</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1506172839506173</v>
+        <v>0.8346913580246914</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9371604938271605</v>
+        <v>0.2796296296296296</v>
       </c>
       <c r="I18" t="n">
-        <v>0.07740740740740741</v>
+        <v>0.9462962962962963</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6459259259259259</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8409876543209877</v>
+        <v>0.3918518518518518</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Rastrigin-20</t>
+          <t>PA-10-20</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>20</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4749382716049383</v>
+        <v>0.05740740740740741</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2469135802469136</v>
+        <v>0.662962962962963</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2864197530864198</v>
+        <v>0.5393827160493827</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2848148148148148</v>
+        <v>0.8351851851851851</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6795061728395062</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9118518518518518</v>
+        <v>0.3045679012345679</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1050617283950617</v>
+        <v>0.9462962962962963</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6592592592592592</v>
+        <v>0.6365432098765432</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8679012345679012</v>
+        <v>0.3658024691358025</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Rastrigin-200</t>
+          <t>PA-10-200</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>200</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4303703703703703</v>
+        <v>0.05740740740740741</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.4822222222222222</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4806172839506173</v>
+        <v>0.7951851851851852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1385185185185185</v>
+        <v>0.7640740740740741</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6992592592592592</v>
+        <v>0.1685185185185185</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9271604938271605</v>
+        <v>0.2796296296296296</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08851851851851852</v>
+        <v>0.9462962962962963</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6235802469135803</v>
+        <v>0.6129629629629629</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8397530864197531</v>
+        <v>0.4103703703703704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Rastrigin-500</t>
+          <t>PA-10-500</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>500</v>
       </c>
       <c r="C21" t="n">
+        <v>0.05740740740740741</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4979012345679013</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8351851851851851</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7240740740740741</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1861728395061728</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2619753086419753</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9462962962962963</v>
       </c>
-      <c r="D21" t="n">
-        <v>0.2791358024691358</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.3907407407407407</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.1282716049382716</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.6228395061728395</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.8181481481481482</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.09814814814814815</v>
-      </c>
       <c r="J21" t="n">
-        <v>0.5023456790123457</v>
+        <v>0.6129629629629629</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7307407407407407</v>
+        <v>0.3946913580246914</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Sphere-100</t>
+          <t>Rastrigin-100</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>100</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05740740740740741</v>
+        <v>0.3835802469135802</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4548148148148148</v>
+        <v>0.2782716049382716</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4377777777777778</v>
+        <v>0.5018518518518519</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2796296296296296</v>
+        <v>0.1351851851851852</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7240740740740741</v>
+        <v>0.6859259259259259</v>
       </c>
       <c r="H22" t="n">
-        <v>0.941358024691358</v>
+        <v>0.9380246913580247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.09925925925925926</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6129629629629629</v>
+        <v>0.6537037037037037</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8401234567901235</v>
+        <v>0.8408641975308642</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Sphere-20</t>
+          <t>Rastrigin-20</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>20</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05740740740740741</v>
+        <v>0.4767901234567901</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4490123456790123</v>
+        <v>0.2383950617283951</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1861728395061728</v>
+        <v>0.2888888888888889</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3565432098765432</v>
+        <v>0.2850617283950617</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6790123456790124</v>
+        <v>0.684320987654321</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8980246913580247</v>
+        <v>0.9141975308641975</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3490123456790123</v>
+        <v>0.1116049382716049</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6580246913580247</v>
+        <v>0.6561728395061729</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8834567901234568</v>
+        <v>0.8612345679012345</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Sphere-200</t>
+          <t>Rastrigin-200</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>200</v>
       </c>
       <c r="C24" t="n">
-        <v>0.05740740740740741</v>
+        <v>0.3704938271604938</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5051851851851852</v>
+        <v>0.2930864197530864</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3913580246913581</v>
+        <v>0.494320987654321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2796296296296296</v>
+        <v>0.1171604938271605</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7753086419753087</v>
+        <v>0.7081481481481482</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9079012345679013</v>
+        <v>0.9345679012345679</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1685185185185185</v>
+        <v>0.1230864197530864</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6090123456790123</v>
+        <v>0.6308641975308642</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8223456790123457</v>
+        <v>0.8449382716049383</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Sphere-500</t>
+          <t>Rastrigin-500</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>500</v>
       </c>
       <c r="C25" t="n">
-        <v>0.167283950617284</v>
+        <v>0.9462962962962963</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8453086419753086</v>
+        <v>0.2788888888888889</v>
       </c>
       <c r="E25" t="n">
         <v>0.3907407407407407</v>
       </c>
       <c r="F25" t="n">
+        <v>0.1362962962962963</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.621358024691358</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8198765432098766</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09037037037037036</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5018518518518519</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.7309876543209877</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-100</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>100</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.05740740740740741</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4776543209876543</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4149382716049383</v>
+      </c>
+      <c r="F26" t="n">
         <v>0.2796296296296296</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.7866666666666666</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.7867901234567901</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.05864197530864197</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="G26" t="n">
+        <v>0.7240740740740741</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9291358024691359</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1685185185185185</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6129629629629629</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.8523456790123457</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-20</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.08061728395061729</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4620987654320988</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.2892592592592593</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.2879012345679012</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6983950617283951</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.912962962962963</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2785185185185185</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.8680246913580247</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-200</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>200</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.07604938271604939</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.5018518518518519</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.3907407407407407</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.2795061728395062</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.8082716049382717</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8916049382716049</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6129629629629629</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.805679012345679</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-500</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>500</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2116049382716049</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.8648148148148148</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2909876543209877</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.3362962962962963</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.7801234567901234</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7796296296296297</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.05740740740740741</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5018518518518519</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.6939506172839506</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sphere-100</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>100</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.05740740740740741</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.4632098765432099</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.4293827160493827</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.2796296296296296</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.7240740740740741</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.9422222222222222</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1685185185185185</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.6129629629629629</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8392592592592593</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Sphere-20</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>20</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.05740740740740741</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4848148148148148</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.177037037037037</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.3417283950617284</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.6769135802469136</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.9012345679012346</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.3371604938271605</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.6601234567901234</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8802469135802469</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Sphere-200</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>200</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.05740740740740741</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5004938271604938</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3920987654320988</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.2796296296296296</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.7804938271604939</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.9101234567901234</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1685185185185185</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.6129629629629629</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.8149382716049383</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Sphere-500</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>500</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1649382716049383</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.884320987654321</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3907407407407407</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.2796296296296296</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.7719753086419753</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.7719753086419753</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.06098765432098766</v>
+      </c>
+      <c r="J33" t="n">
         <v>0.5055555555555555</v>
       </c>
-      <c r="K25" t="n">
-        <v>0.6960493827160494</v>
+      <c r="K33" t="n">
+        <v>0.6865432098765432</v>
       </c>
     </row>
   </sheetData>
